--- a/docs/เทียบราคาขายแยกก้อน-R4.1.xlsx
+++ b/docs/เทียบราคาขายแยกก้อน-R4.1.xlsx
@@ -293,7 +293,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -356,7 +356,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="7">
@@ -419,7 +419,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="5">
       <c r="A5" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="7">
@@ -545,7 +545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="7">
@@ -671,7 +671,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="7">
@@ -797,7 +797,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="11">
       <c r="A11" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="7">
@@ -923,7 +923,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="7">
@@ -1049,7 +1049,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="15">
       <c r="A15" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="7">
@@ -1175,7 +1175,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1238,7 +1238,7 @@
     <row r="17">
       <c r="A17" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="7">
@@ -1301,7 +1301,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="7">
@@ -1427,7 +1427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="7">
@@ -1553,7 +1553,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="7">
@@ -1679,7 +1679,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1742,7 +1742,7 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="7">
@@ -1805,7 +1805,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="7">
@@ -1931,7 +1931,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1994,7 +1994,7 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="7">
@@ -2057,7 +2057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="7">
@@ -2183,7 +2183,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2246,7 +2246,7 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="7">
@@ -2309,7 +2309,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2372,7 +2372,7 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="7">
@@ -2435,7 +2435,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="7">
@@ -2561,7 +2561,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2624,7 +2624,7 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="7">
@@ -2687,7 +2687,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2750,7 +2750,7 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="7">
@@ -2813,7 +2813,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="7">
@@ -2939,7 +2939,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="7">
@@ -3065,7 +3065,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="7">
@@ -3191,7 +3191,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="7">
@@ -3317,7 +3317,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3380,7 +3380,7 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="7">
@@ -3443,7 +3443,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="7">
@@ -3569,7 +3569,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="7">
@@ -3695,7 +3695,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3758,7 +3758,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="7">
@@ -3821,7 +3821,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3884,7 +3884,7 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="7">
@@ -3947,7 +3947,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="7">
@@ -4073,7 +4073,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="7">
@@ -4199,7 +4199,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4262,7 +4262,7 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเลือนกระจก5+5</t>
+          <t xml:space="preserve">หลังคาเลื่อน (เปิด-ปิดได้)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="7">
@@ -4325,7 +4325,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="7">
@@ -4451,7 +4451,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4514,7 +4514,7 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="7">
@@ -4577,7 +4577,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4640,7 +4640,7 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="7">
@@ -4703,7 +4703,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="7">
@@ -4829,7 +4829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4892,7 +4892,7 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="7">
@@ -4955,7 +4955,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5018,7 +5018,7 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="7">
@@ -5081,7 +5081,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5144,7 +5144,7 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="7">
@@ -5207,7 +5207,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5270,7 +5270,7 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="7">
@@ -5333,7 +5333,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="7">
@@ -5459,7 +5459,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5522,7 +5522,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="7">
@@ -5585,7 +5585,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="7">
@@ -5711,7 +5711,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนง1"×1.6"โชว์1.6"</t>
+          <t xml:space="preserve">ระแนงบังตา</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="7">
@@ -5837,7 +5837,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="7">
@@ -5953,7 +5953,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6011,7 +6011,7 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="7">
@@ -6069,7 +6069,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6127,7 +6127,7 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="7">
@@ -6185,7 +6185,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="7">
@@ -6301,7 +6301,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="7">
@@ -6417,7 +6417,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="7">
@@ -6533,7 +6533,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6591,7 +6591,7 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนรางบน</t>
+          <t xml:space="preserve">บานเลื่อนรางบน</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="7">
@@ -6649,7 +6649,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="7">
@@ -6765,7 +6765,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6823,7 +6823,7 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="7">
@@ -6881,7 +6881,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="7">
@@ -6997,7 +6997,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7055,7 +7055,7 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="7">
@@ -7113,7 +7113,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7171,7 +7171,7 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="7">
@@ -7229,7 +7229,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7287,7 +7287,7 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="7">
@@ -7345,7 +7345,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7403,7 +7403,7 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSlimLux</t>
+          <t xml:space="preserve">บานเลื่อนเฟรมบาง SlimLux</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="7">
@@ -7461,7 +7461,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7519,7 +7519,7 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="7">
@@ -7577,7 +7577,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7635,7 +7635,7 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="7">
@@ -7693,7 +7693,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7751,7 +7751,7 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="7">
@@ -7809,7 +7809,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7867,7 +7867,7 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="7">
@@ -7925,7 +7925,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="7">
@@ -8041,7 +8041,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8099,7 +8099,7 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="7">
@@ -8157,7 +8157,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8215,7 +8215,7 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="7">
@@ -8273,7 +8273,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8331,7 +8331,7 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="7">
@@ -8389,7 +8389,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8447,7 +8447,7 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนยูโร</t>
+          <t xml:space="preserve">บานเลื่อน ยูโร</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="7">
@@ -8505,7 +8505,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8568,7 +8568,7 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="7">
@@ -8631,7 +8631,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8694,7 +8694,7 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="7">
@@ -8757,7 +8757,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8820,7 +8820,7 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="7">
@@ -8883,7 +8883,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8946,7 +8946,7 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="7">
@@ -9009,7 +9009,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9072,7 +9072,7 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="7">
@@ -9135,7 +9135,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9198,7 +9198,7 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="7">
@@ -9261,7 +9261,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9324,7 +9324,7 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="7">
@@ -9387,7 +9387,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9450,7 +9450,7 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ประตูรัวระแนงสลับ</t>
+          <t xml:space="preserve">ประตูรั้วบานเลื่อน</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="7">
@@ -9513,7 +9513,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงหมุน</t>
+          <t xml:space="preserve">ระแนงปรับหมุนได้</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9571,7 +9571,7 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงหมุน</t>
+          <t xml:space="preserve">ระแนงปรับหมุนได้</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="7">
@@ -9629,7 +9629,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงหมุน</t>
+          <t xml:space="preserve">ระแนงปรับหมุนได้</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9687,7 +9687,7 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงหมุน</t>
+          <t xml:space="preserve">ระแนงปรับหมุนได้</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="7">
@@ -9745,7 +9745,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงหมุน</t>
+          <t xml:space="preserve">ระแนงปรับหมุนได้</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9803,7 +9803,7 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงหมุน</t>
+          <t xml:space="preserve">ระแนงปรับหมุนได้</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="7">
@@ -9861,7 +9861,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานตู้Futuretech</t>
+          <t xml:space="preserve">ฝาตู้ Future Tech (เฉพาะบานหน้า)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9919,7 +9919,7 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานตู้Futuretech</t>
+          <t xml:space="preserve">ฝาตู้ Future Tech (เฉพาะบานหน้า)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="7">
@@ -9971,7 +9971,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานตู้Futuretech</t>
+          <t xml:space="preserve">ฝาตู้ Future Tech (เฉพาะบานหน้า)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10029,7 +10029,7 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานตู้Futuretech</t>
+          <t xml:space="preserve">ฝาตู้ Future Tech (เฉพาะบานหน้า)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="7">
@@ -10081,7 +10081,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานตู้Futuretech</t>
+          <t xml:space="preserve">ฝาตู้ Future Tech (เฉพาะบานหน้า)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานตู้Futuretech</t>
+          <t xml:space="preserve">ฝาตู้ Future Tech (เฉพาะบานหน้า)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="7">
@@ -10191,7 +10191,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยม</t>
+          <t xml:space="preserve">บานเฟี้ยม</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10249,7 +10249,7 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยม</t>
+          <t xml:space="preserve">บานเฟี้ยม</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="7">
@@ -10307,7 +10307,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยม</t>
+          <t xml:space="preserve">บานเฟี้ยม</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยม</t>
+          <t xml:space="preserve">บานเฟี้ยม</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="7">
@@ -10423,7 +10423,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยม</t>
+          <t xml:space="preserve">บานเฟี้ยม</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10481,7 +10481,7 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยม</t>
+          <t xml:space="preserve">บานเฟี้ยม</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="7">
@@ -10539,7 +10539,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยมยูโร</t>
+          <t xml:space="preserve">บานเฟี้ยม ยูโร</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10597,7 +10597,7 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยมยูโร</t>
+          <t xml:space="preserve">บานเฟี้ยม ยูโร</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="7">
@@ -10655,7 +10655,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยมยูโร</t>
+          <t xml:space="preserve">บานเฟี้ยม ยูโร</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10713,7 +10713,7 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยมยูโร</t>
+          <t xml:space="preserve">บานเฟี้ยม ยูโร</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="7">
@@ -10771,7 +10771,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยมยูโร</t>
+          <t xml:space="preserve">บานเฟี้ยม ยูโร</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยมยูโร</t>
+          <t xml:space="preserve">บานเฟี้ยม ยูโร</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="7">
@@ -10887,7 +10887,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10950,7 +10950,7 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="7">
@@ -11013,7 +11013,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11076,7 +11076,7 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="7">
@@ -11139,7 +11139,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11202,7 +11202,7 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="7">
@@ -11265,7 +11265,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="7">
@@ -11391,7 +11391,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11454,7 +11454,7 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="7">
@@ -11517,7 +11517,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11580,7 +11580,7 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="7">
@@ -11643,7 +11643,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11706,7 +11706,7 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="7">
@@ -11769,7 +11769,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11832,7 +11832,7 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="7">
@@ -11895,7 +11895,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11958,7 +11958,7 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="7">
@@ -12021,7 +12021,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12084,7 +12084,7 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="7">
@@ -12147,7 +12147,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12210,7 +12210,7 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="7">
@@ -12273,7 +12273,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12336,7 +12336,7 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="7">
@@ -12399,7 +12399,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12462,7 +12462,7 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="7">
@@ -12525,7 +12525,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12588,7 +12588,7 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="7">
@@ -12651,7 +12651,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12714,7 +12714,7 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="7">
@@ -12777,7 +12777,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12840,7 +12840,7 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="7">
@@ -12903,7 +12903,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="7">
@@ -13029,7 +13029,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13092,7 +13092,7 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="7">
@@ -13155,7 +13155,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13218,7 +13218,7 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="7">
@@ -13281,7 +13281,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13344,7 +13344,7 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="7">
@@ -13407,7 +13407,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13470,7 +13470,7 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="7">
@@ -13533,7 +13533,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13596,7 +13596,7 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="7">
@@ -13659,7 +13659,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13722,7 +13722,7 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="7">
@@ -13785,7 +13785,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13848,7 +13848,7 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="7">
@@ -13911,7 +13911,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="7">
@@ -14037,7 +14037,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14100,7 +14100,7 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="7">
@@ -14163,7 +14163,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14226,7 +14226,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="7">
@@ -14289,7 +14289,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14352,7 +14352,7 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="7">
@@ -14415,7 +14415,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14478,7 +14478,7 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="7">
@@ -14541,7 +14541,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14604,7 +14604,7 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="7">
@@ -14667,7 +14667,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14730,7 +14730,7 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="7">
@@ -14793,7 +14793,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14856,7 +14856,7 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="7">
@@ -14919,7 +14919,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -14982,7 +14982,7 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="7">
@@ -15045,7 +15045,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15108,7 +15108,7 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="7">
@@ -15171,7 +15171,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15234,7 +15234,7 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="7">
@@ -15297,7 +15297,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15360,7 +15360,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาเพิงกระจก5+5</t>
+          <t xml:space="preserve">หลังคา</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="7">
@@ -15423,7 +15423,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15486,7 +15486,7 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="7">
@@ -15549,7 +15549,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15612,7 +15612,7 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="7">
@@ -15675,7 +15675,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15738,7 +15738,7 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="7">
@@ -15801,7 +15801,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15864,7 +15864,7 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="7">
@@ -15927,7 +15927,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -15990,7 +15990,7 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="7">
@@ -16053,7 +16053,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16116,7 +16116,7 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="7">
@@ -16179,7 +16179,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16242,7 +16242,7 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="7">
@@ -16305,7 +16305,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16368,7 +16368,7 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="7">
@@ -16431,7 +16431,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16494,7 +16494,7 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="7">
@@ -16557,7 +16557,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16620,7 +16620,7 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="7">
@@ -16683,7 +16683,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16746,7 +16746,7 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="7">
@@ -16809,7 +16809,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16872,7 +16872,7 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="7">
@@ -16935,7 +16935,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -16998,7 +16998,7 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="7">
@@ -17061,7 +17061,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17124,7 +17124,7 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="7">
@@ -17187,7 +17187,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17250,7 +17250,7 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="7">
@@ -17313,7 +17313,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17376,7 +17376,7 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="7">
@@ -17439,7 +17439,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17502,7 +17502,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="7">
@@ -17565,7 +17565,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17628,7 +17628,7 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="7">
@@ -17691,7 +17691,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17754,7 +17754,7 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="7">
@@ -17817,7 +17817,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17880,7 +17880,7 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="7">
@@ -17943,7 +17943,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="7">
@@ -18069,7 +18069,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18132,7 +18132,7 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="7">
@@ -18195,7 +18195,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18258,7 +18258,7 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="7">
@@ -18321,7 +18321,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18384,7 +18384,7 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="7">
@@ -18447,7 +18447,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18510,7 +18510,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="7">
@@ -18573,7 +18573,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18636,7 +18636,7 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="7">
@@ -18699,7 +18699,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18762,7 +18762,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="7">
@@ -18825,7 +18825,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18888,7 +18888,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="7">
@@ -18951,7 +18951,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19014,7 +19014,7 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="7">
@@ -19077,7 +19077,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19140,7 +19140,7 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="7">
@@ -19203,7 +19203,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19266,7 +19266,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="7">
@@ -19329,7 +19329,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19392,7 +19392,7 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="7">
@@ -19455,7 +19455,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19518,7 +19518,7 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="7">
@@ -19581,7 +19581,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19644,7 +19644,7 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="7">
@@ -19707,7 +19707,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19770,7 +19770,7 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="7">
@@ -19833,7 +19833,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19896,7 +19896,7 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">หลังคาจัวกระจก5+5</t>
+          <t xml:space="preserve">หลังคาจั่ว</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="7">
@@ -19959,7 +19959,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20017,7 +20017,7 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="7">
@@ -20075,7 +20075,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20133,7 +20133,7 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="7">
@@ -20191,7 +20191,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20249,7 +20249,7 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="7">
@@ -20307,7 +20307,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20365,7 +20365,7 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="7">
@@ -20423,7 +20423,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20481,7 +20481,7 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="7">
@@ -20539,7 +20539,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20597,7 +20597,7 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="7">
@@ -20655,7 +20655,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20713,7 +20713,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="7">
@@ -20771,7 +20771,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20829,7 +20829,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="7">
@@ -20887,7 +20887,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20945,7 +20945,7 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนSMS</t>
+          <t xml:space="preserve">บานเลื่อน SMS</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="7">
@@ -21003,7 +21003,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21061,7 +21061,7 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="7">
@@ -21119,7 +21119,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21177,7 +21177,7 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="7">
@@ -21235,7 +21235,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21293,7 +21293,7 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="7">
@@ -21351,7 +21351,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21409,7 +21409,7 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="7">
@@ -21467,7 +21467,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21525,7 +21525,7 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="7">
@@ -21583,7 +21583,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21641,7 +21641,7 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="7">
@@ -21699,7 +21699,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21757,7 +21757,7 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="7">
@@ -21815,7 +21815,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21873,7 +21873,7 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="7">
@@ -21931,7 +21931,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -21989,7 +21989,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเลือนEseries</t>
+          <t xml:space="preserve">บานเลื่อน E-series</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="7">
@@ -22047,7 +22047,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22105,7 +22105,7 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="7">
@@ -22163,7 +22163,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22221,7 +22221,7 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="7">
@@ -22279,7 +22279,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22337,7 +22337,7 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="7">
@@ -22395,7 +22395,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -22453,7 +22453,7 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="7">
@@ -22511,7 +22511,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22569,7 +22569,7 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="7">
@@ -22627,7 +22627,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -22685,7 +22685,7 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="7">
@@ -22743,7 +22743,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -22801,7 +22801,7 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="7">
@@ -22859,7 +22859,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22917,7 +22917,7 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="7">
@@ -22975,7 +22975,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23033,7 +23033,7 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานระแนงเลือน(ลูกฟูกเรียบ2ทางแนวตัง)</t>
+          <t xml:space="preserve">ระแนงเลื่อน (ลูกฟูกเรียบ 2 ทาง · ข้อ 38.2)</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="7">
@@ -23091,7 +23091,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23151,7 +23151,7 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="7">
@@ -23208,7 +23208,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23268,7 +23268,7 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="7">
@@ -23325,7 +23325,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -23385,7 +23385,7 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="7">
@@ -23442,7 +23442,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -23502,7 +23502,7 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="7">
@@ -23559,7 +23559,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -23619,7 +23619,7 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="7">
@@ -23676,7 +23676,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23736,7 +23736,7 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="7">
@@ -23793,7 +23793,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -23853,7 +23853,7 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="7">
@@ -23910,7 +23910,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -23970,7 +23970,7 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="7">
@@ -24027,7 +24027,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24087,7 +24087,7 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ชุดShower+บานเลือน</t>
+          <t xml:space="preserve">ห้องอาบน้ำ Shower (กระจกเทมเปอร์)</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="7">
@@ -24144,7 +24144,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24202,7 +24202,7 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="7">
@@ -24260,7 +24260,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -24318,7 +24318,7 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="7">
@@ -24376,7 +24376,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="7">
@@ -24492,7 +24492,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -24550,7 +24550,7 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="7">
@@ -24608,7 +24608,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -24666,7 +24666,7 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="7">
@@ -24724,7 +24724,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -24782,7 +24782,7 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปด</t>
+          <t xml:space="preserve">บานเปิด</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="7">
@@ -24840,7 +24840,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -24900,7 +24900,7 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="7">
@@ -24960,7 +24960,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -25020,7 +25020,7 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="7">
@@ -25080,7 +25080,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25140,7 +25140,7 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="7">
@@ -25200,7 +25200,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -25260,7 +25260,7 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="7">
@@ -25320,7 +25320,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -25380,7 +25380,7 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="7">
@@ -25440,7 +25440,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -25500,7 +25500,7 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานเปลือยบานเปด</t>
+          <t xml:space="preserve">บานเปลือย (ติดตาย/สวิง/เลื่อน)</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="7">
@@ -25560,7 +25560,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -25623,7 +25623,7 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="7">
@@ -25686,7 +25686,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -25749,7 +25749,7 @@
     <row r="419">
       <c r="A419" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="7">
@@ -25812,7 +25812,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -25875,7 +25875,7 @@
     <row r="421">
       <c r="A421" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="7">
@@ -25938,7 +25938,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -26001,7 +26001,7 @@
     <row r="423">
       <c r="A423" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="7">
@@ -26064,7 +26064,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -26127,7 +26127,7 @@
     <row r="425">
       <c r="A425" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="7">
@@ -26190,7 +26190,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -26253,7 +26253,7 @@
     <row r="427">
       <c r="A427" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานโซลิด1</t>
+          <t xml:space="preserve">บานโซลิด</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="7">
@@ -26316,7 +26316,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -26374,7 +26374,7 @@
     <row r="429">
       <c r="A429" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="7">
@@ -26432,7 +26432,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -26490,7 +26490,7 @@
     <row r="431">
       <c r="A431" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="7">
@@ -26548,7 +26548,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -26606,7 +26606,7 @@
     <row r="433">
       <c r="A433" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="7">
@@ -26664,7 +26664,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -26722,7 +26722,7 @@
     <row r="435">
       <c r="A435" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ระแนงสลับ</t>
+          <t xml:space="preserve">ระแนงสลับ (คละกล่อง 2 แบบ)</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="7">
@@ -26780,7 +26780,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานหมุน</t>
+          <t xml:space="preserve">บานหมุน (Pivot)</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -26838,7 +26838,7 @@
     <row r="437">
       <c r="A437" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานหมุน</t>
+          <t xml:space="preserve">บานหมุน (Pivot)</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="7">
@@ -26896,7 +26896,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานหมุน</t>
+          <t xml:space="preserve">บานหมุน (Pivot)</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="439">
       <c r="A439" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานหมุน</t>
+          <t xml:space="preserve">บานหมุน (Pivot)</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="7">
@@ -27012,7 +27012,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t xml:space="preserve">บานหมุน</t>
+          <t xml:space="preserve">บานหมุน (Pivot)</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -27070,7 +27070,7 @@
     <row r="441">
       <c r="A441" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">บานหมุน</t>
+          <t xml:space="preserve">บานหมุน (Pivot)</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="7">
@@ -27128,7 +27128,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCDoor</t>
+          <t xml:space="preserve">ประตูบานเปิด PC Door</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -27186,7 +27186,7 @@
     <row r="443">
       <c r="A443" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">PCDoor</t>
+          <t xml:space="preserve">ประตูบานเปิด PC Door</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="7">
@@ -27244,7 +27244,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCDoor</t>
+          <t xml:space="preserve">ประตูบานเปิด PC Door</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -27302,7 +27302,7 @@
     <row r="445">
       <c r="A445" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">PCDoor</t>
+          <t xml:space="preserve">ประตูบานเปิด PC Door</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="7">
@@ -27360,7 +27360,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCDoor</t>
+          <t xml:space="preserve">ประตูบานเปิด PC Door</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -27418,7 +27418,7 @@
     <row r="447">
       <c r="A447" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">PCDoor</t>
+          <t xml:space="preserve">ประตูบานเปิด PC Door</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="7">
@@ -27476,7 +27476,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velora</t>
+          <t xml:space="preserve">Velora บานเปิด</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -27534,7 +27534,7 @@
     <row r="449">
       <c r="A449" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">Velora</t>
+          <t xml:space="preserve">Velora บานเปิด</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="7">
@@ -27592,7 +27592,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velora</t>
+          <t xml:space="preserve">Velora บานเปิด</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -27650,7 +27650,7 @@
     <row r="451">
       <c r="A451" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">Velora</t>
+          <t xml:space="preserve">Velora บานเปิด</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="7">
@@ -27708,7 +27708,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velora</t>
+          <t xml:space="preserve">Velora บานเปิด</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="453">
       <c r="A453" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">Velora</t>
+          <t xml:space="preserve">Velora บานเปิด</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="7">
@@ -28868,7 +28868,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยมยก</t>
+          <t xml:space="preserve">บานเฟี้ยมยก</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -28926,7 +28926,7 @@
     <row r="473">
       <c r="A473" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยมยก</t>
+          <t xml:space="preserve">บานเฟี้ยมยก</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="7">
@@ -28984,7 +28984,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยมยก</t>
+          <t xml:space="preserve">บานเฟี้ยมยก</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -29042,7 +29042,7 @@
     <row r="475">
       <c r="A475" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยมยก</t>
+          <t xml:space="preserve">บานเฟี้ยมยก</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="7">
@@ -29100,7 +29100,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t xml:space="preserve">เฟยมยก</t>
+          <t xml:space="preserve">บานเฟี้ยมยก</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -29158,7 +29158,7 @@
     <row r="477">
       <c r="A477" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เฟยมยก</t>
+          <t xml:space="preserve">บานเฟี้ยมยก</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="7">
@@ -29216,7 +29216,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t xml:space="preserve">ติดตาย</t>
+          <t xml:space="preserve">บานติดตาย</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -29274,7 +29274,7 @@
     <row r="479">
       <c r="A479" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ติดตาย</t>
+          <t xml:space="preserve">บานติดตาย</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="7">
@@ -29332,7 +29332,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t xml:space="preserve">ติดตาย</t>
+          <t xml:space="preserve">บานติดตาย</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="481">
       <c r="A481" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ติดตาย</t>
+          <t xml:space="preserve">บานติดตาย</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="7">
@@ -29448,7 +29448,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t xml:space="preserve">ติดตาย</t>
+          <t xml:space="preserve">บานติดตาย</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -29506,7 +29506,7 @@
     <row r="483">
       <c r="A483" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ติดตาย</t>
+          <t xml:space="preserve">บานติดตาย</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="7">
@@ -29564,7 +29564,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตายดัดโค้ง</t>
+          <t xml:space="preserve">บานติดตายดัดโค้ง</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -29622,7 +29622,7 @@
     <row r="485">
       <c r="A485" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ตายดัดโค้ง</t>
+          <t xml:space="preserve">บานติดตายดัดโค้ง</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="7">
@@ -29680,7 +29680,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตายดัดโค้ง</t>
+          <t xml:space="preserve">บานติดตายดัดโค้ง</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -29738,7 +29738,7 @@
     <row r="487">
       <c r="A487" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ตายดัดโค้ง</t>
+          <t xml:space="preserve">บานติดตายดัดโค้ง</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="7">
@@ -29796,7 +29796,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตายดัดโค้ง</t>
+          <t xml:space="preserve">บานติดตายดัดโค้ง</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -29854,7 +29854,7 @@
     <row r="489">
       <c r="A489" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ตายดัดโค้ง</t>
+          <t xml:space="preserve">บานติดตายดัดโค้ง</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="7">
@@ -29912,7 +29912,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t xml:space="preserve">เปดดัดโค้ง</t>
+          <t xml:space="preserve">บานเปิดดัดโค้ง</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -29970,7 +29970,7 @@
     <row r="491">
       <c r="A491" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เปดดัดโค้ง</t>
+          <t xml:space="preserve">บานเปิดดัดโค้ง</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="7">
@@ -30028,7 +30028,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t xml:space="preserve">เปดดัดโค้ง</t>
+          <t xml:space="preserve">บานเปิดดัดโค้ง</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="493">
       <c r="A493" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เปดดัดโค้ง</t>
+          <t xml:space="preserve">บานเปิดดัดโค้ง</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="7">
@@ -30144,7 +30144,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t xml:space="preserve">เปดดัดโค้ง</t>
+          <t xml:space="preserve">บานเปิดดัดโค้ง</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -30202,7 +30202,7 @@
     <row r="495">
       <c r="A495" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">เปดดัดโค้ง</t>
+          <t xml:space="preserve">บานเปิดดัดโค้ง</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="7">
@@ -30260,7 +30260,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t xml:space="preserve">ราวกันตก</t>
+          <t xml:space="preserve">ราวกันตก/ราวบันได กระจก</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -30318,7 +30318,7 @@
     <row r="497">
       <c r="A497" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ราวกันตก</t>
+          <t xml:space="preserve">ราวกันตก/ราวบันได กระจก</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="7">
@@ -30376,7 +30376,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t xml:space="preserve">ราวกันตก</t>
+          <t xml:space="preserve">ราวกันตก/ราวบันได กระจก</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -30434,7 +30434,7 @@
     <row r="499">
       <c r="A499" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ราวกันตก</t>
+          <t xml:space="preserve">ราวกันตก/ราวบันได กระจก</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="7">
@@ -30492,7 +30492,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t xml:space="preserve">ราวกันตก</t>
+          <t xml:space="preserve">ราวกันตก/ราวบันได กระจก</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -30550,7 +30550,7 @@
     <row r="501">
       <c r="A501" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">ราวกันตก</t>
+          <t xml:space="preserve">ราวกันตก/ราวบันได กระจก</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="7">
